--- a/data/dividends_info_20261021.xlsx
+++ b/data/dividends_info_20261021.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41.88999938964844</v>
+        <v>42.01499938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2148484156393666</v>
+        <v>0.2142092141078883</v>
       </c>
       <c r="J2" t="n">
         <v>145</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59.20000076293945</v>
+        <v>59</v>
       </c>
       <c r="I3" t="n">
-        <v>1.182432417193846</v>
+        <v>1.186440677966102</v>
       </c>
       <c r="J3" t="n">
         <v>124</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.739999771118164</v>
+        <v>8.779999732971191</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6864988738131719</v>
+        <v>0.6833713191890466</v>
       </c>
       <c r="J4" t="n">
         <v>54</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41.875</v>
+        <v>42.01499938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2149253731343284</v>
+        <v>0.2142092141078883</v>
       </c>
       <c r="J6" t="n">
         <v>54</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J7" t="n">
         <v>33</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.607843137254902</v>
+        <v>0.6019417475728156</v>
       </c>
       <c r="J8" t="n">
         <v>33</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>26.25</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I9" t="n">
-        <v>1.028571428571429</v>
+        <v>1.022727287505284</v>
       </c>
       <c r="J9" t="n">
         <v>33</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.8700008392334</v>
+        <v>26.1299991607666</v>
       </c>
       <c r="I10" t="n">
-        <v>2.280633864940699</v>
+        <v>2.257941136430907</v>
       </c>
       <c r="J10" t="n">
         <v>33</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.46000003814697</v>
+        <v>10.39999961853027</v>
       </c>
       <c r="I11" t="n">
-        <v>2.007648176234637</v>
+        <v>2.019230843295715</v>
       </c>
       <c r="J11" t="n">
         <v>26</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.940000057220459</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I12" t="n">
-        <v>3.367003334568775</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J12" t="n">
         <v>26</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.880000114440918</v>
+        <v>7.760000228881836</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7614213087388637</v>
+        <v>0.7731958534831846</v>
       </c>
       <c r="J14" t="n">
         <v>19</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.78999996185303</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="I15" t="n">
-        <v>4.263206687917371</v>
+        <v>4.255318983755513</v>
       </c>
       <c r="J15" t="n">
         <v>5</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.079999923706055</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4702970341436654</v>
+        <v>0.4846938681175491</v>
       </c>
       <c r="J19" t="n">
         <v>-23</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>26.25</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I20" t="n">
-        <v>1.028571428571429</v>
+        <v>1.022727287505284</v>
       </c>
       <c r="J20" t="n">
         <v>-30</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.947999954223633</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I21" t="n">
-        <v>2.926078097507816</v>
+        <v>2.923076851598377</v>
       </c>
       <c r="J21" t="n">
         <v>-30</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>41.875</v>
+        <v>42.01499938964844</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2149253731343284</v>
+        <v>0.2142092141078883</v>
       </c>
       <c r="J22" t="n">
         <v>-30</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>92.44999694824219</v>
+        <v>94</v>
       </c>
       <c r="I23" t="n">
-        <v>1.438615515308882</v>
+        <v>1.414893617021277</v>
       </c>
       <c r="J23" t="n">
         <v>-30</v>
@@ -1583,14 +1583,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1821,14 +1821,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1872,14 +1872,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1889,14 +1889,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1913,7 +1913,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1940,14 +1940,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1964,7 +1964,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2025,14 +2025,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2049,7 +2049,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2076,14 +2076,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2093,14 +2093,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2127,14 +2127,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2144,14 +2144,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2304,7 +2304,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2331,14 +2331,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2348,14 +2348,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2440,7 +2440,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2457,7 +2457,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2535,14 +2535,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2569,14 +2569,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2654,14 +2654,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2671,14 +2671,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2688,14 +2688,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2722,14 +2722,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3028,14 +3028,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3062,14 +3062,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3103,7 +3103,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3113,14 +3113,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3137,7 +3137,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3181,14 +3181,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3205,7 +3205,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3232,14 +3232,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3273,7 +3273,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3290,7 +3290,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3324,7 +3324,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3334,14 +3334,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3392,7 +3392,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3409,7 +3409,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3555,14 +3555,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3579,7 +3579,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3681,7 +3681,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3749,7 +3749,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3759,14 +3759,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3783,7 +3783,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3868,7 +3868,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3885,7 +3885,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3895,14 +3895,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3946,14 +3946,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4004,7 +4004,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4014,14 +4014,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4038,7 +4038,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4065,14 +4065,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4089,7 +4089,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4133,14 +4133,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4225,7 +4225,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4242,7 +4242,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4293,7 +4293,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4320,14 +4320,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4337,14 +4337,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4388,14 +4388,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4480,7 +4480,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4507,14 +4507,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4548,7 +4548,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4575,14 +4575,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4609,14 +4609,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4667,7 +4667,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4718,7 +4718,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4735,7 +4735,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4786,7 +4786,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4837,7 +4837,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4854,7 +4854,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4871,7 +4871,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4888,7 +4888,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4905,7 +4905,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4956,7 +4956,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4966,14 +4966,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5068,14 +5068,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5170,14 +5170,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5245,7 +5245,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5255,14 +5255,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5296,7 +5296,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5330,7 +5330,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5340,14 +5340,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5357,14 +5357,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5398,7 +5398,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5415,7 +5415,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5432,7 +5432,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5466,7 +5466,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5483,7 +5483,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5510,14 +5510,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5527,14 +5527,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5578,14 +5578,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5619,7 +5619,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5697,14 +5697,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5748,14 +5748,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5799,14 +5799,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5823,7 +5823,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5840,7 +5840,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5857,7 +5857,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5874,7 +5874,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5908,7 +5908,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5969,14 +5969,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5986,14 +5986,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6003,14 +6003,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6027,7 +6027,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6133,95 +6133,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nabla S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PLANETEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>